--- a/data/input/astroEntity.xlsx
+++ b/data/input/astroEntity.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22540" windowHeight="11480"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="entity_tracking" sheetId="1" r:id="rId1"/>
@@ -30,275 +30,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
   <si>
     <t>Procyon</t>
-  </si>
-  <si>
-    <t>van Maanen 2</t>
-  </si>
-  <si>
-    <t>Hubble Space Telescope</t>
-  </si>
-  <si>
-    <t>Five-hundred-meter Aperture Spherical Telescope</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>SN 1987A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>SN 1572</t>
-  </si>
-  <si>
-    <t>SN 2011fe</t>
-  </si>
-  <si>
-    <t>Hyades (star cluster)</t>
-  </si>
-  <si>
-    <t>Omega Centauri</t>
-  </si>
-  <si>
-    <t>Betelgeuse</t>
-  </si>
-  <si>
-    <t>Sirius</t>
-  </si>
-  <si>
-    <t>Voyager program</t>
-  </si>
-  <si>
-    <t>Curiosity (rover)</t>
-  </si>
-  <si>
-    <t>Solar Orbiter</t>
-  </si>
-  <si>
-    <t>International Space Station</t>
-  </si>
-  <si>
-    <t>Starlink</t>
-  </si>
-  <si>
-    <t>ULAS J1342+0928</t>
-  </si>
-  <si>
-    <t>3C 273</t>
-  </si>
-  <si>
-    <t>PSR J0337+1715</t>
-  </si>
-  <si>
-    <t>Helix Nebula</t>
-  </si>
-  <si>
-    <t>Ring Nebula</t>
-  </si>
-  <si>
-    <t>Mars</t>
-  </si>
-  <si>
-    <t>Venus</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>PSR J0348+0432</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>PSR B1919+21</t>
-  </si>
-  <si>
-    <t>Crab Nebula</t>
-  </si>
-  <si>
-    <t>Eagle Nebula</t>
-  </si>
-  <si>
-    <t>Europa (moon)</t>
-  </si>
-  <si>
-    <t>Titan (moon)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Perseids</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Leonids</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>Orion Nebula</t>
-  </si>
-  <si>
-    <t>Orion Molecular Cloud Complex</t>
-  </si>
-  <si>
-    <t>Andromeda Galaxy</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Triangulum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>LHS 1140 b</t>
-  </si>
-  <si>
-    <t>Gliese 581g</t>
-  </si>
-  <si>
-    <t>Comet NEOWISE</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Halley's Comet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>Messier 87</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Sagittarius A*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>Big Bang</t>
-  </si>
-  <si>
-    <t>Lambda-CDM model</t>
-  </si>
-  <si>
-    <t>Hertzsprung-Russell Diagram</t>
-  </si>
-  <si>
-    <t>Nebular Hypothesis</t>
-  </si>
-  <si>
-    <t>Zhang Heng</t>
-  </si>
-  <si>
-    <t>Galileo Galilei</t>
-  </si>
-  <si>
-    <t>Stephen Hawking</t>
-  </si>
-  <si>
-    <t>101955 Bennu</t>
-  </si>
-  <si>
-    <t>4 Vesta</t>
   </si>
 </sst>
 </file>
@@ -920,15 +660,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1203,13 +940,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1470,260 +1200,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="35.5" customWidth="1"/>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" ht="15" spans="1:1">
-      <c r="A2" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:1">
-      <c r="A3" s="1" t="s">
+    <row r="2" ht="14.25" spans="1:2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" ht="15" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" ht="15" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" ht="15" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" ht="15" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" ht="15" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="1:1">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="15" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" ht="15" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" ht="15" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="1:1">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="15" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" ht="15" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="1:1">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" ht="15" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" ht="15" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" ht="15" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" ht="15" spans="1:1">
-      <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" ht="15" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" ht="15" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" ht="15" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" ht="15" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" ht="15" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" ht="15" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" ht="15" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" ht="15" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" ht="15" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" ht="15" spans="1:1">
-      <c r="A44" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" ht="15" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" ht="15" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" ht="15" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" ht="15" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" ht="15" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" ht="15" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>49</v>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
